--- a/tools/xlsform_samples/KDQOL-36.xlsx
+++ b/tools/xlsform_samples/KDQOL-36.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>These questions are about how you feel and how things have been with you during the past 4 weeks. For each question, please give the one answer that comes closest to the way you have been feeling. How much of the time during the past 4 weeks…</t>
+          <t>These questions are about how you feel and how things have been with you during the past 4 weeks. For each question, please give the one answer that comes closest to the way you have been feeling. How much of the time during the past 4 weeks...</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>burden_kidney (mean_coded) - Mean of 4 burden items (1=Definitely true … 5=Definitely false; all negative-worded so reverse-code). Higher = less burden. Reverse code: (1+5)−response, then (mean−1)/4×1</t>
+          <t>burden_kidney (mean_coded) - Mean of 4 burden items (1=Definitely true ... 5=Definitely false; all negative-worded so reverse-code). Higher = less burden. Reverse code: (1+5)-response, then (mean-1)/4</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>symptoms_problems (mean_coded) - Mean of 12 symptom items (items 28a/28b optional, not scored). Columns: 1=Not at all…5=Extremely; reverse-coded so 5=not bothered. Transform: (mean−1)/4×100 → 0–100.</t>
+          <t>symptoms_problems (mean_coded) - Mean of 12 symptom items (items 28a/28b optional, not scored). Columns: 1=Not at all...5=Extremely; reverse-coded so 5=not bothered. Transform: (mean-1)/4x100 -&gt; 0-100</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>effects_daily_life (mean_coded) - Mean of 8 effects items. Values pre-reversed (Not limited=5). 0–100: (mean − 1) / 4 × 100.</t>
+          <t>effects_daily_life (mean_coded) - Mean of 8 effects items. Values pre-reversed (Not limited=5). 0-100: (mean - 1) / 4 x 100.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>

--- a/tools/xlsform_samples/KDQOL-36.xlsx
+++ b/tools/xlsform_samples/KDQOL-36.xlsx
@@ -442,11 +442,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -1872,28 +1872,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>KDQOL_36_scoring</t>
+          <t>KDQOL_36_sf12_physical</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Computed Scores</t>
+          <t>sf12_physical (sum_coded) - SF-12 Physical Component Summary (PCS). Computed from relevant SF-12 items using the SF-12 scoring algorithm (Ware et al., 1996). Score is standardized to a mean of 50 (SD=</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>${kdqol36_1} + ${kdqol36_2} + ${kdqol36_3} + ${kdqol36_4} + ${kdqol36_5} + ${kdqol36_8}</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KDQOL_36_burden_kidney</t>
+          <t>KDQOL_36_sf12_mental</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>burden_kidney (mean_coded) - Mean of 4 burden items (1=Definitely true ... 5=Definitely false; all negative-worded so reverse-code). Higher = less burden. Reverse code: (1+5)-response, then (mean-1)/4</t>
+          <t>sf12_mental (sum_coded) - SF-12 Mental Component Summary (MCS). Computed from relevant SF-12 items using the SF-12 scoring algorithm (Ware et al., 1996). Score is standardized to a mean of 50 (SD=10).</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1920,7 +1920,7 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>(((((6 - ${kdqol36_burden_grid_1}) + (6 - ${kdqol36_burden_grid_2}) + (6 - ${kdqol36_burden_grid_3}) + (6 - ${kdqol36_burden_grid_4})) div 4) - 1) div 4) * 100</t>
+          <t>${kdqol36_1} + ${kdqol36_6} + ${kdqol36_7} + ${kdqol36_8}</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>KDQOL_36_symptoms_problems</t>
+          <t>KDQOL_36_overall_health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>symptoms_problems (mean_coded) - Mean of 12 symptom items (items 28a/28b optional, not scored). Columns: 1=Not at all...5=Extremely; reverse-coded so 5=not bothered. Transform: (mean-1)/4x100 -&gt; 0-100</t>
+          <t>overall_health (sum_coded) - SF-12 social functioning item. Response: 1=All of the time to 5=None of the time. Part of the SF-12 algorithm (see sf12_physical and sf12_mental).</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1950,7 +1950,7 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>(((((6 - ${kdqol36_symp_grid_1}) + (6 - ${kdqol36_symp_grid_2}) + (6 - ${kdqol36_symp_grid_3}) + (6 - ${kdqol36_symp_grid_4}) + (6 - ${kdqol36_symp_grid_5}) + (6 - ${kdqol36_symp_grid_6}) + (6 - ${kdqol36_symp_grid_7}) + (6 - ${kdqol36_symp_grid_8}) + (6 - ${kdqol36_symp_grid_9}) + (6 - ${kdqol36_symp_grid_10}) + (6 - ${kdqol36_symp_grid_11}) + (6 - ${kdqol36_symp_grid_12})) div 12) - 1) div 4) * 100</t>
+          <t>${kdqol36_12}</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -1958,148 +1958,6 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>KDQOL_36_effects_daily_life</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>effects_daily_life (mean_coded) - Mean of 8 effects items. Values pre-reversed (Not limited=5). 0-100: (mean - 1) / 4 x 100.</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>(((((6 - ${kdqol36_eff_grid_1}) + (6 - ${kdqol36_eff_grid_2}) + (6 - ${kdqol36_eff_grid_3}) + (6 - ${kdqol36_eff_grid_4}) + (6 - ${kdqol36_eff_grid_5}) + (6 - ${kdqol36_eff_grid_6}) + (6 - ${kdqol36_eff_grid_7}) + (6 - ${kdqol36_eff_grid_8})) div 8) - 1) div 4) * 100</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>KDQOL_36_sf12_physical</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>sf12_physical (sum_coded) - SF-12 Physical Component Summary (PCS). Computed from relevant SF-12 items using the SF-12 scoring algorithm (Ware et al., 1996). Score is standardized to a mean of 50 (SD=</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>${kdqol36_1} + ${kdqol36_2} + ${kdqol36_3} + ${kdqol36_4} + ${kdqol36_5} + ${kdqol36_8} + ${kdqol36_mh_grid_1} + (6 - ${kdqol36_mh_grid_2}) + ${kdqol36_mh_grid_3}</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>KDQOL_36_sf12_mental</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>sf12_mental (sum_coded) - SF-12 Mental Component Summary (MCS). Computed from relevant SF-12 items using the SF-12 scoring algorithm (Ware et al., 1996). Score is standardized to a mean of 50 (SD=10).</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>${kdqol36_1} + ${kdqol36_6} + ${kdqol36_7} + ${kdqol36_8} + ${kdqol36_mh_grid_1} + (6 - ${kdqol36_mh_grid_2}) + ${kdqol36_mh_grid_3}</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>KDQOL_36_overall_health</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>overall_health (sum_coded) - SF-12 social functioning item. Response: 1=All of the time to 5=None of the time. Part of the SF-12 algorithm (see sf12_physical and sf12_mental).</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>${kdqol36_12}</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>KDQOL_36_scoring</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tools/xlsform_samples/KDQOL-36.xlsx
+++ b/tools/xlsform_samples/KDQOL-36.xlsx
@@ -2903,7 +2903,11 @@
           <t>20260618</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>English (en)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
